--- a/data/trans_orig/P79A7_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P79A7_2023-Provincia-trans_orig.xlsx
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7987</t>
+          <t>9015</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>14661</t>
+          <t>16345</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7987</t>
+          <t>9015</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7987</t>
+          <t>9015</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7987</t>
+          <t>9015</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>14661</t>
+          <t>16345</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>14661</t>
+          <t>16345</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>14661</t>
+          <t>16345</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,27 +2097,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>9047</t>
+          <t>10147</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12372</t>
+          <t>13226</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2167,27 +2167,27 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>15721</t>
+          <t>17477</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10286</t>
+          <t>11459</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19046</t>
+          <t>20556</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>7263</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2290,12 +2290,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8760</t>
+          <t>9097</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>44,25%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12372</t>
+          <t>13226</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12372</t>
+          <t>13226</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12372</t>
+          <t>13226</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>19046</t>
+          <t>20556</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>19046</t>
+          <t>20556</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>19046</t>
+          <t>20556</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
